--- a/dentipro_data.xlsx
+++ b/dentipro_data.xlsx
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1409,6 +1409,45 @@
       <c r="I13" s="34" t="inlineStr">
         <is>
           <t>13/04/2026 22:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="34" t="n">
+        <v>25</v>
+      </c>
+      <c r="B14" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>Benali Achraf</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>Carie</t>
+        </is>
+      </c>
+      <c r="G14" s="34" t="inlineStr"/>
+      <c r="H14" s="34" t="inlineStr">
+        <is>
+          <t>Prevu</t>
+        </is>
+      </c>
+      <c r="I14" s="34" t="inlineStr">
+        <is>
+          <t>15/04/2026 16:37</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2676,6 +2715,41 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="35" t="inlineStr">
+        <is>
+          <t>15/04/2026 16:37</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="inlineStr">
+        <is>
+          <t>📅 RDV AJOUT</t>
+        </is>
+      </c>
+      <c r="D22" s="36" t="inlineStr">
+        <is>
+          <t>RDV planifié</t>
+        </is>
+      </c>
+      <c r="E22" s="35" t="inlineStr">
+        <is>
+          <t>Benali Achraf</t>
+        </is>
+      </c>
+      <c r="F22" s="35" t="inlineStr">
+        <is>
+          <t>15/04/2026 à 17:00:00 — Carie</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="inlineStr">
+        <is>
+          <t>Système</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>

--- a/dentipro_data.xlsx
+++ b/dentipro_data.xlsx
@@ -871,7 +871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1451,6 +1451,49 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="34" t="n">
+        <v>26</v>
+      </c>
+      <c r="B15" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>Benali Achraf</t>
+        </is>
+      </c>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>Carie</t>
+        </is>
+      </c>
+      <c r="G15" s="34" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H15" s="34" t="inlineStr">
+        <is>
+          <t>Prevu</t>
+        </is>
+      </c>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t>17/04/2026 18:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
@@ -1464,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1721,6 +1764,46 @@
       <c r="J6" s="25" t="inlineStr">
         <is>
           <t>09/04/2026 14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Ameur Yassine</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Especes</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>FAC-00004</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="23" t="inlineStr"/>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>15/04/2026 21:01</t>
         </is>
       </c>
     </row>
@@ -1937,10 +2020,10 @@
         <v>900</v>
       </c>
       <c r="I4" s="38" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="J4" s="38" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K4" s="39" t="inlineStr">
         <is>
@@ -1949,7 +2032,7 @@
       </c>
       <c r="L4" s="34" t="inlineStr">
         <is>
-          <t>09/04/2026 14:15</t>
+          <t>15/04/2026 21:01</t>
         </is>
       </c>
     </row>
@@ -1966,7 +2049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2750,6 +2833,111 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>15/04/2026 21:01</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>💰 PAIEMENT AJOUT</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Paiement reçu</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
+        <is>
+          <t>Ameur Yassine</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
+        <is>
+          <t>100.00 DH — Especes | Fac.FAC-00004</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>Système</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
+        <is>
+          <t>15/04/2026 21:01</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>🔄 FACTURE MAJ</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>Facture mise à jour</t>
+        </is>
+      </c>
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>Ameur Yassine</t>
+        </is>
+      </c>
+      <c r="F24" s="27" t="inlineStr">
+        <is>
+          <t>FAC-00004 | Payé: 600.00 DH | Reste: 300.00 DH | Partiellement payee</t>
+        </is>
+      </c>
+      <c r="G24" s="27" t="inlineStr">
+        <is>
+          <t>Système</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="35" t="inlineStr">
+        <is>
+          <t>17/04/2026 18:03</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="inlineStr">
+        <is>
+          <t>📅 RDV AJOUT</t>
+        </is>
+      </c>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>RDV planifié</t>
+        </is>
+      </c>
+      <c r="E25" s="35" t="inlineStr">
+        <is>
+          <t>Benali Achraf</t>
+        </is>
+      </c>
+      <c r="F25" s="35" t="inlineStr">
+        <is>
+          <t>17/04/2026 à 19:00:00 — Carie</t>
+        </is>
+      </c>
+      <c r="G25" s="35" t="inlineStr">
+        <is>
+          <t>Système</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" copies="1"/>
